--- a/光伏配储项目/电价数据/2026/旗鼓岭站.xlsx
+++ b/光伏配储项目/电价数据/2026/旗鼓岭站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7054199999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56468</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51261</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45465</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43925</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40213</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41286</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41303</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26133</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21455</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25856</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07686</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06354</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05184</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03181</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05353</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03841</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02623</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08588</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01977</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00306</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14476</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21277</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23484</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18534</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11535</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01605</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.009949999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.11514</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11762</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.17462</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.17271</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.14633</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1211</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19164</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.01248</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.22797</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.01179</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45826</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52695</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48169</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.73934</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6107899999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.51335</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.51337</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.57913</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5389299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5017699999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.5975499999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5571499999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47984</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42211</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62493</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.42496</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74429</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.01009</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79892</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5367799999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52398</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50664</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50671</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5022300000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47431</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51661</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6291</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7202200000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43743</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09074</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.0419</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26424</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26978</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.60711</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.21125</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.58309</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01189</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.17383</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23598</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.24202</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23222</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25071</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.24987</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6873899999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7934099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7870499999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8035099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.77706</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43547</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.58949</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43289</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33343</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51513</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46561</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44812</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.13969</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.25207</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.24821</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07302</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21698</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15145</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20934</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19669</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24904</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.20676</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47833</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.00099</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5029399999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34339</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47014</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13456</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.12999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.09551999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26694</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22641</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13031</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21508</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04107</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04519</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06537999999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.21237</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.05609</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.00521</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00182</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.08288</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.1159</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25307</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19499</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22342</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18229</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23204</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23638</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25233</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.27473</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48486</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29097</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04013000000000001</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04534000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04458</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04661</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04183</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04604999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04443</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04703</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04496</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04695000000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05134</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05351</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00259</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14646</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03687</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09842000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6635700000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04629</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.0458</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04259</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03195</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04138</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10653</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03766</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04221</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04429</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04151</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04132</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03983</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04493</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04186</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04685</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20146</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27044</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33698</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32077</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17361</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15986</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17243</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16065</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15995</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23838</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21537</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22792</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27106</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26937</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.89228</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.3112</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.91525</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63614</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2143</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8821</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5655399999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35883</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05208</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5589400000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81498</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7970900000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79667</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87974</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88647</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5156900000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42885</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47568</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23595</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87966</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55153</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65055</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54548</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50595</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45933</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44221</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58868</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59661</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65607</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45158</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5591499999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8619199999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6532899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.82896</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81192</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84862</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9865499999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54362</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6116</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.45817</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16456</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20053</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27497</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27546</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35044</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14053</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70726</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65232</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58761</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.54961</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.06087</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6838500000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04351</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6579299999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21857</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.5356599999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26537</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26562</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58608</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7159099999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43868</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42461</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32568</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23582</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14492</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14724</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15409</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14438</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14077</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14415</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14259</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14468</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14212</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03406</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11414</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14535</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14148</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14665</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35007</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5494</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46974</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42478</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.24031</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18392</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24025</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22111</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24636</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22115</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36054</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03764</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25199</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25005</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19995</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18042</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24472</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25075</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4690299999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7330599999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30104</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34935</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.6005499999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43958</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.70256</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.92636</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.49419</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34506</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13428</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2840299999999999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19482</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24519</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02255</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11288</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02256</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23074</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24047</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14422</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20981</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21711</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.71045</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6669400000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6617000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.69084</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.88017</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46662</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48316</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.50226</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.44294</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.51344</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.49378</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48678</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42696</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46473</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.46492</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26763</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12711</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00375</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.01005</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6616299999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.12246</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08534</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.03884000000000001</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.25917</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.00532</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43985</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.53342</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.53577</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.62276</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7685700000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.7512799999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.74003</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8401799999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58693</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.55252</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.91552</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.83774</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.65747</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.71717</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43096</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4659700000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49233</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5730499999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.47483</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43685</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.46293</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.47436</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.41348</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.46571</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1557</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27484</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04747</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45396</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46464</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04225</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18366</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36406</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23417</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23433</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13272</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23295</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01085</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15998</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25613</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00411</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14521</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15355</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.03029</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.03983</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21737</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22945</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.15309</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21554</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26735</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26362</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35227</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22699</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21705</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15115</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18009</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.07926000000000001</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00154</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04268</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.06419</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03327</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03265</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04831000000000001</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16971</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21486</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24477</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24643</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26545</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25517</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26672</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05618</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06522</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24932</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22528</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22524</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26979</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26135</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24357</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22208</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20627</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18954</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22608</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16983</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.18993</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22315</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21983</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24434</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23227</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21508</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26134</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2257</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26903</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24663</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24962</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18412</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06493</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49164</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.5490900000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22925</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.01949</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20253</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09384999999999999</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04317</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05633</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00643</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20825</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03267</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.00301</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02718</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13097</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03854</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04111</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.08259999999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02663</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02926</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04834</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28222</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25516</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.22463</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.14776</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24805</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11398</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25848</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26975</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16727</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.15025</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33119</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.50963</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50651</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17024</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27943</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23811</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.2775899999999999</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47836</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.05918</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.7413099999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36899</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.24033</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17574</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46627</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5619700000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55822</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49811</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53711</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.73097</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77366</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55013</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55228</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37565</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28065</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26028</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21053</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23492</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.16596</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.00146</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14241</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.03379</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.15061</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01037</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02338</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.0403</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02254</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03372</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02646</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02747</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01458</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.03152</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12274</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.07962000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.13362</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.20023</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19154</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.16399</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3785</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.81375</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.25222</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22385</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.22292</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08979000000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.12176</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03117</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.006549999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01638</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00831</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01324</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15483</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.18293</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03568</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.17807</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.15975</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18734</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.20232</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.2289</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.25662</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45866</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.51737</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38595</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.52324</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21843</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12698</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17629</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20069</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09828000000000001</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12542</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05984</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07962999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04355</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04484</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06906999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03022</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08309</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.16084</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10205</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20916</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18268</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04731</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23733</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10183</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15631</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.19188</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20219</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17333</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21173</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23775</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49567</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40942</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38416</v>
       </c>
     </row>
   </sheetData>
